--- a/results/Int Task Remove ACC -0.1/Rando_5_permute.xlsx
+++ b/results/Int Task Remove ACC -0.1/Rando_5_permute.xlsx
@@ -440,427 +440,427 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8008329591798555</v>
+        <v>0.8238125303999702</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.806659931904067</v>
+        <v>0.8192427133610207</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.806659931904067</v>
+        <v>0.825755322333221</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8192632918022973</v>
+        <v>0.8258226699592173</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8192632918022973</v>
+        <v>0.8286695102330977</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8230595465259849</v>
+        <v>0.7905792831219367</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8250009353836943</v>
+        <v>0.7906012646387548</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8177615332809518</v>
+        <v>0.7931389606016388</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7934794402663973</v>
+        <v>0.7855258727129869</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.801316552549856</v>
+        <v>0.7853486175028996</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7817113780072585</v>
+        <v>0.7853486175028996</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.754021682194036</v>
+        <v>0.7855918172634415</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7297381861039398</v>
+        <v>0.786673120814158</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7082150072959927</v>
+        <v>0.7694368054776068</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.718435944924608</v>
+        <v>0.7643833950686572</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7187670707524226</v>
+        <v>0.7731465372095634</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7304663823100235</v>
+        <v>0.775905451416171</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7294730048265798</v>
+        <v>0.7615599393871366</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7294510233097616</v>
+        <v>0.7622661540764022</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7297162045871217</v>
+        <v>0.7582500841845325</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7395386687619262</v>
+        <v>0.7720006921839339</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6956088412466794</v>
+        <v>0.7832122011449096</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7237325550940996</v>
+        <v>0.7853308452127062</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7268459797208815</v>
+        <v>0.793273188161784</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.723821884236914</v>
+        <v>0.7891266322445467</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7130911624948554</v>
+        <v>0.7891266322445467</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.680794701986755</v>
+        <v>0.7542690911812024</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7125827814569536</v>
+        <v>0.7694115501178584</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6923841059602649</v>
+        <v>0.7762772664346915</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6900662251655629</v>
+        <v>0.7672489430164253</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6937086092715232</v>
+        <v>0.7672489430164253</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6937086092715232</v>
+        <v>0.7775854005312979</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.708676619149175</v>
+        <v>0.7791091405694616</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6983677554532869</v>
+        <v>0.7821084483855277</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6890742507576608</v>
+        <v>0.8098336887791372</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6834670932016313</v>
+        <v>0.7509138698694204</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6646368840498372</v>
+        <v>0.7465035357503649</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6692726456392413</v>
+        <v>0.7515569461593146</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6699788603285067</v>
+        <v>0.7198198451004603</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6699788603285067</v>
+        <v>0.6324746511018819</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6673957982564448</v>
+        <v>0.6096559658772028</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6681239944625286</v>
+        <v>0.6096559658772028</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6836209638193587</v>
+        <v>0.6384447375313353</v>
       </c>
     </row>
     <row r="45">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6578151307666404</v>
+        <v>0.6130855501926891</v>
       </c>
     </row>
     <row r="46">
@@ -880,447 +880,447 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6208169641186815</v>
+        <v>0.6029553447824297</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.622318722640027</v>
+        <v>0.5751379690949228</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6207070565345905</v>
+        <v>0.5914936206832042</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6319653346802858</v>
+        <v>0.6565738766041831</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6438419014479739</v>
+        <v>0.6552054102592884</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.669140756538332</v>
+        <v>0.653218655292401</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6684345418490665</v>
+        <v>0.6540539529314925</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6718996707449396</v>
+        <v>0.6282743106222173</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6608845923597859</v>
+        <v>0.6849361132936731</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6608845923597859</v>
+        <v>0.687848898118008</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6571790698544543</v>
+        <v>0.6836102069068731</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6571790698544543</v>
+        <v>0.6798621244434466</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7113312380738579</v>
+        <v>0.6319503685411756</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7323474389194448</v>
+        <v>0.6213543420511094</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7309350095409137</v>
+        <v>0.6091026864219703</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7243344745014404</v>
+        <v>0.6091026864219703</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7219038799715644</v>
+        <v>0.5971821566206458</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7211990683578404</v>
+        <v>0.5866109177984808</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7629279380401841</v>
+        <v>0.5865449732480263</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7580709582070566</v>
+        <v>0.5892599244209975</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6541975343285815</v>
+        <v>0.55965643356905</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5653005387810079</v>
+        <v>0.5639334755116548</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5619878774273207</v>
+        <v>0.5523880345717813</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5619878774273207</v>
+        <v>0.5470446552175703</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5603322482882478</v>
+        <v>0.528192464548958</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5490080255920979</v>
+        <v>0.5027603172821491</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5638221648520223</v>
+        <v>0.5026943727316945</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5625416245744004</v>
+        <v>0.5019661765256108</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5563367568376548</v>
+        <v>0.5020101395592472</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5745486773674562</v>
+        <v>0.5009068544917125</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5804429977176637</v>
+        <v>0.5382155685262094</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5773969207168781</v>
+        <v>0.539186964492835</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5515691061473417</v>
+        <v>0.5369789912822239</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5600245070527931</v>
+        <v>0.577487652935234</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5596494181913421</v>
+        <v>0.5711522991731208</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5646822501590152</v>
+        <v>0.5692754517903243</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5624317169903095</v>
+        <v>0.5378170950723987</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5421081677704194</v>
+        <v>0.5146453025030867</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5421081677704194</v>
+        <v>0.5156372769109889</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5323175066412242</v>
+        <v>0.5034473566056796</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5250121599880271</v>
+        <v>0.495636435065664</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5389208478317806</v>
+        <v>0.4989434841171849</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5385457589703296</v>
+        <v>0.4989434841171849</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5051871702772477</v>
+        <v>0.5006210947730759</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4950527556403637</v>
+        <v>0.5023412653870617</v>
       </c>
     </row>
   </sheetData>
